--- a/data/trans_dic/IP16A05-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A05-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos</t>
+          <t>Menores que consumiero medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 22,26</t>
+          <t>2,56; 24,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,54; 33,56</t>
+          <t>6,15; 33,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 32,08</t>
+          <t>3,53; 37,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,75</t>
+          <t>0,0; 33,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,0</t>
+          <t>0,0; 20,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,69</t>
+          <t>0,0; 23,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,26</t>
+          <t>0,0; 36,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,44</t>
+          <t>0,0; 33,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 17,61</t>
+          <t>2,67; 15,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,12; 23,59</t>
+          <t>5,9; 22,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 25,41</t>
+          <t>2,68; 24,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 26,6</t>
+          <t>3,27; 26,5</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 16,27</t>
+          <t>5,36; 16,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,52; 26,38</t>
+          <t>12,22; 26,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,55; 16,78</t>
+          <t>6,27; 16,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,11; 16,59</t>
+          <t>3,28; 16,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,47; 16,2</t>
+          <t>5,33; 15,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,48; 19,81</t>
+          <t>8,04; 19,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 19,62</t>
+          <t>7,19; 19,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,84</t>
+          <t>1,38; 7,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,59; 13,93</t>
+          <t>6,6; 14,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,14; 20,83</t>
+          <t>11,67; 20,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,13; 15,72</t>
+          <t>8,49; 16,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 9,7</t>
+          <t>3,15; 11,06</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,03</t>
+          <t>0,0; 17,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,71; 29,22</t>
+          <t>8,41; 28,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 27,52</t>
+          <t>5,72; 28,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 16,85</t>
+          <t>2,88; 17,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 23,87</t>
+          <t>5,5; 24,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,92; 26,35</t>
+          <t>5,67; 26,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,83; 28,18</t>
+          <t>5,03; 28,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 19,52</t>
+          <t>2,08; 17,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 18,18</t>
+          <t>5,37; 17,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,08; 23,81</t>
+          <t>9,71; 24,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,39; 24,76</t>
+          <t>8,27; 24,01</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 15,92</t>
+          <t>4,23; 14,49</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 13,73</t>
+          <t>5,14; 13,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,88; 23,92</t>
+          <t>12,83; 23,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 16,59</t>
+          <t>7,72; 16,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,64; 14,54</t>
+          <t>4,53; 14,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,57; 15,22</t>
+          <t>6,99; 14,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,82; 18,12</t>
+          <t>8,86; 17,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,73; 18,77</t>
+          <t>8,27; 18,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 9,11</t>
+          <t>3,17; 9,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,91; 12,77</t>
+          <t>6,7; 12,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,25; 19,17</t>
+          <t>12,25; 19,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,44; 16,06</t>
+          <t>9,47; 16,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,64; 10,42</t>
+          <t>4,72; 9,94</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3834</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1964</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1843</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3326</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5138</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2629</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3643</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>565; 5420</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1418; 7668</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>554; 5850</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5158</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4126</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4065</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3241</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5276</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1131; 6743</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2395; 9202</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>656; 5995</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1010; 8187</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>7832</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16464</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8737</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9533</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8832</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>13482</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11031</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4095</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>16664</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>29946</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>19768</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>13628</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4329; 13156</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>10778; 23358</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5205; 13609</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>3968; 19417</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4676; 13602</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>8124; 19649</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>6155; 17007</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1662; 8575</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>11121; 23617</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>22095; 39558</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>14319; 28165</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>7577; 26631</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6077</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4194</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3637</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4547</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5679</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4362</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3903</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>5847</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>11756</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>8557</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>7540</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4008</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3061; 10231</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1647; 8124</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1198; 7308</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1941; 8606</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2238; 10324</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1453; 8265</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>967; 8367</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3105; 10393</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7366; 18917</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4771; 13842</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3732; 12774</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>11155</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>26375</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14895</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15013</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>14682</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>20465</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>16058</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>9798</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>25837</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>46840</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>30953</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>24812</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>6445; 17141</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>18949; 34234</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>9846; 21561</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>8044; 25937</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>10004; 21407</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>13999; 28216</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>10193; 23328</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>5777; 17076</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>17991; 33951</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>37430; 58313</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>23748; 40852</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>16992; 35777</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A05-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A05-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 24,58</t>
+          <t>2,55; 24,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,15; 33,25</t>
+          <t>7,23; 31,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 37,28</t>
+          <t>3,48; 33,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,87</t>
+          <t>0,0; 33,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,37</t>
+          <t>0,0; 20,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,23</t>
+          <t>0,0; 22,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,89</t>
+          <t>0,0; 34,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,67</t>
+          <t>0,0; 34,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 15,94</t>
+          <t>2,82; 15,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,9; 22,69</t>
+          <t>6,04; 23,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 24,49</t>
+          <t>2,64; 25,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 26,5</t>
+          <t>3,34; 25,84</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,36; 16,3</t>
+          <t>5,91; 16,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,22; 26,47</t>
+          <t>12,86; 26,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,27; 16,4</t>
+          <t>6,54; 16,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 16,07</t>
+          <t>3,34; 17,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 15,52</t>
+          <t>5,7; 15,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,04; 19,45</t>
+          <t>8,42; 19,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,19; 19,86</t>
+          <t>8,29; 19,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 7,14</t>
+          <t>1,49; 6,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 14,03</t>
+          <t>6,53; 14,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,67; 20,9</t>
+          <t>11,59; 20,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,49; 16,71</t>
+          <t>8,39; 16,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 11,06</t>
+          <t>3,11; 10,4</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,77</t>
+          <t>0,0; 18,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,41; 28,1</t>
+          <t>8,49; 28,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,72; 28,21</t>
+          <t>5,18; 27,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 17,55</t>
+          <t>3,37; 17,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,5; 24,4</t>
+          <t>5,46; 24,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,67; 26,18</t>
+          <t>6,67; 25,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 28,63</t>
+          <t>6,69; 30,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 17,99</t>
+          <t>2,18; 19,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 17,98</t>
+          <t>5,3; 17,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,71; 24,95</t>
+          <t>9,09; 22,89</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,27; 24,01</t>
+          <t>8,32; 25,01</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 14,49</t>
+          <t>4,41; 15,62</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 13,68</t>
+          <t>5,27; 13,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,83; 23,18</t>
+          <t>12,97; 23,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,72; 16,92</t>
+          <t>7,5; 16,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 14,59</t>
+          <t>4,49; 14,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 14,95</t>
+          <t>6,53; 14,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,86; 17,86</t>
+          <t>9,09; 18,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,27; 18,92</t>
+          <t>8,47; 19,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 9,37</t>
+          <t>2,99; 9,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 12,64</t>
+          <t>6,86; 12,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,25; 19,08</t>
+          <t>12,03; 19,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,47; 16,29</t>
+          <t>9,13; 16,05</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 9,94</t>
+          <t>4,51; 10,02</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>565; 5420</t>
+          <t>562; 5473</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1418; 7668</t>
+          <t>1666; 7287</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>554; 5850</t>
+          <t>545; 5295</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5158</t>
+          <t>0; 5161</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4126</t>
+          <t>0; 4148</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4065</t>
+          <t>0; 4012</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3241</t>
+          <t>0; 3035</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5276</t>
+          <t>0; 5337</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1131; 6743</t>
+          <t>1191; 6757</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2395; 9202</t>
+          <t>2451; 9344</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>656; 5995</t>
+          <t>647; 6327</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1010; 8187</t>
+          <t>1033; 7983</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4329; 13156</t>
+          <t>4770; 13419</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10778; 23358</t>
+          <t>11348; 23308</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5205; 13609</t>
+          <t>5429; 13792</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3968; 19417</t>
+          <t>4034; 20822</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4676; 13602</t>
+          <t>4998; 13968</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8124; 19649</t>
+          <t>8508; 19765</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6155; 17007</t>
+          <t>7098; 16697</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1662; 8575</t>
+          <t>1787; 7896</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11121; 23617</t>
+          <t>10989; 23749</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22095; 39558</t>
+          <t>21935; 39088</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14319; 28165</t>
+          <t>14142; 27279</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7577; 26631</t>
+          <t>7495; 25047</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4008</t>
+          <t>0; 4090</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3061; 10231</t>
+          <t>3089; 10495</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1647; 8124</t>
+          <t>1492; 7993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1198; 7308</t>
+          <t>1401; 7204</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1941; 8606</t>
+          <t>1925; 8695</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2238; 10324</t>
+          <t>2631; 10039</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1453; 8265</t>
+          <t>1932; 8776</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>967; 8367</t>
+          <t>1015; 8869</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3105; 10393</t>
+          <t>3065; 9893</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7366; 18917</t>
+          <t>6890; 17362</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4771; 13842</t>
+          <t>4797; 14421</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3732; 12774</t>
+          <t>3886; 13770</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6445; 17141</t>
+          <t>6600; 17356</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18949; 34234</t>
+          <t>19150; 34373</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9846; 21561</t>
+          <t>9561; 20678</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8044; 25937</t>
+          <t>7984; 25286</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10004; 21407</t>
+          <t>9344; 20777</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13999; 28216</t>
+          <t>14362; 29524</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10193; 23328</t>
+          <t>10447; 23916</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5777; 17076</t>
+          <t>5454; 16563</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17991; 33951</t>
+          <t>18427; 34454</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37430; 58313</t>
+          <t>36772; 58807</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23748; 40852</t>
+          <t>22883; 40249</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16992; 35777</t>
+          <t>16231; 36075</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A05-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A05-Estudios-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
+          <t>Menores que consumieron medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13,36%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>9,17%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>16,63%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>12,52%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,1%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,57%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 24,82</t>
+          <t>0,0; 20,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,23; 31,6</t>
+          <t>0,0; 24,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 33,74</t>
+          <t>0,0; 41,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,89</t>
+          <t>0,0; 36,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,48</t>
+          <t>2,62; 22,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,92</t>
+          <t>7,54; 33,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,54</t>
+          <t>3,48; 32,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,07</t>
+          <t>3,26; 40,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 15,97</t>
+          <t>3,09; 17,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 23,04</t>
+          <t>6,12; 23,59</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 25,85</t>
+          <t>3,32; 25,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 25,84</t>
+          <t>5,0; 30,6</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10,07%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13,34%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12,88%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>9,7%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>18,66%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>10,53%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,89%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>10,07%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>13,34%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,88%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,91; 16,63</t>
+          <t>5,47; 16,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,86; 26,42</t>
+          <t>8,48; 19,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,54; 16,62</t>
+          <t>7,46; 19,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 17,23</t>
+          <t>1,34; 6,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 15,93</t>
+          <t>5,45; 16,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,42; 19,56</t>
+          <t>12,52; 26,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,29; 19,5</t>
+          <t>5,55; 16,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 6,58</t>
+          <t>3,9; 13,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,53; 14,1</t>
+          <t>6,59; 13,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,59; 20,65</t>
+          <t>12,14; 20,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,39; 16,18</t>
+          <t>8,13; 15,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,11; 10,4</t>
+          <t>3,17; 8,1</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12,89%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14,4%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15,11%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8,41%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,77%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>16,69%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>14,57%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15,11%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,14</t>
+          <t>5,6; 23,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,49; 28,83</t>
+          <t>5,92; 26,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 27,76</t>
+          <t>6,83; 28,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 17,3</t>
+          <t>2,17; 19,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,46; 24,66</t>
+          <t>0,0; 17,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,67; 25,46</t>
+          <t>7,71; 29,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 30,4</t>
+          <t>6,0; 27,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 19,07</t>
+          <t>2,64; 16,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,3; 17,11</t>
+          <t>4,61; 18,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,09; 22,89</t>
+          <t>9,08; 23,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,32; 25,01</t>
+          <t>8,39; 24,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,41; 15,62</t>
+          <t>4,37; 15,75</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10,25%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12,96%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13,03%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8,9%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>17,86%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>11,69%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,25%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,96%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,03%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,27; 13,85</t>
+          <t>6,57; 15,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,97; 23,27</t>
+          <t>8,82; 18,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,5; 16,22</t>
+          <t>8,73; 18,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 14,23</t>
+          <t>2,82; 9,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,53; 14,51</t>
+          <t>5,51; 13,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,09; 18,69</t>
+          <t>12,88; 23,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,47; 19,4</t>
+          <t>7,52; 16,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 9,09</t>
+          <t>5,36; 12,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,86; 12,83</t>
+          <t>6,91; 12,77</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,03; 19,24</t>
+          <t>12,25; 19,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,13; 16,05</t>
+          <t>9,44; 16,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,51; 10,02</t>
+          <t>4,6; 9,34</t>
         </is>
       </c>
     </row>
@@ -1246,13 +1246,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
+          <t>Menores que consumieron medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>3834</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1964</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1843</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3416</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>562; 5473</t>
+          <t>0; 4051</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1666; 7287</t>
+          <t>0; 4321</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>545; 5295</t>
+          <t>0; 3625</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5161</t>
+          <t>0; 5041</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4148</t>
+          <t>577; 4908</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4012</t>
+          <t>1740; 7739</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3035</t>
+          <t>547; 5034</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5337</t>
+          <t>319; 3943</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1191; 6757</t>
+          <t>1307; 7450</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2451; 9344</t>
+          <t>2482; 9567</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>647; 6327</t>
+          <t>812; 6218</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1033; 7983</t>
+          <t>1184; 7252</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8832</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13482</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11031</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3450</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>7832</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>16464</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>8737</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9533</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8832</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13482</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11031</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>6972</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>10422</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4770; 13419</t>
+          <t>4798; 14199</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11348; 23308</t>
+          <t>8563; 20015</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5429; 13792</t>
+          <t>6384; 16795</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4034; 20822</t>
+          <t>1451; 7071</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4998; 13968</t>
+          <t>4400; 13132</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8508; 19765</t>
+          <t>11050; 23273</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7098; 16697</t>
+          <t>4608; 13923</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1787; 7896</t>
+          <t>3614; 12058</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10989; 23749</t>
+          <t>11099; 23463</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21935; 39088</t>
+          <t>22978; 39427</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14142; 27279</t>
+          <t>13712; 26503</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7495; 25047</t>
+          <t>6368; 16250</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4547</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5679</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4362</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3625</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1301</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>6077</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>4194</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3637</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4547</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5679</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4362</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>3383</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7008</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4090</t>
+          <t>1975; 8418</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3089; 10495</t>
+          <t>2334; 10392</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1492; 7993</t>
+          <t>1971; 8135</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1401; 7204</t>
+          <t>937; 8532</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1925; 8695</t>
+          <t>0; 3841</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2631; 10039</t>
+          <t>2805; 10639</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1932; 8776</t>
+          <t>1728; 7922</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1015; 8869</t>
+          <t>1072; 6601</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3065; 9893</t>
+          <t>2664; 10511</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6890; 17362</t>
+          <t>6885; 18053</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4797; 14421</t>
+          <t>4839; 14278</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3886; 13770</t>
+          <t>3659; 13172</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14682</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20465</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16058</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8935</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>11155</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>26375</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>14895</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>15013</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>14682</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20465</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>16058</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24812</t>
+          <t>20846</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6600; 17356</t>
+          <t>9414; 21796</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19150; 34373</t>
+          <t>13930; 28618</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9561; 20678</t>
+          <t>10764; 23141</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7984; 25286</t>
+          <t>4658; 15696</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9344; 20777</t>
+          <t>6900; 17203</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14362; 29524</t>
+          <t>19018; 35328</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10447; 23916</t>
+          <t>9591; 21149</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5454; 16563</t>
+          <t>7662; 18239</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18427; 34454</t>
+          <t>18564; 34274</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36772; 58807</t>
+          <t>37446; 58597</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22883; 40249</t>
+          <t>23666; 40267</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16231; 36075</t>
+          <t>14164; 28753</t>
         </is>
       </c>
     </row>
